--- a/olympic_simulator/media/simulacion_AFC Champions League Elite_1880.xlsx
+++ b/olympic_simulator/media/simulacion_AFC Champions League Elite_1880.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Al Shamal SC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -551,7 +551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al Shorta SC</t>
+          <t>Ajman FC</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -567,13 +567,13 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="8">
@@ -608,70 +608,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Al Shamal SC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Ajman FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Al Shorta SC</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Ajman FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Al Shorta SC</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Al Shamal SC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Ajman FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Al Shamal SC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -680,37 +680,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Ajman FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Al Shorta SC</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Al Shamal SC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Vissel Kobe</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Al Shorta SC</t>
-        </is>
-      </c>
       <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
         <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -803,13 +803,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
         <v>17</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -818,29 +818,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -849,29 +849,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
       </c>
       <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
         <v>11</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -880,7 +880,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -893,16 +893,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="n">
         <v>15</v>
       </c>
-      <c r="H6" t="n">
-        <v>12</v>
-      </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="7">
@@ -911,29 +911,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -942,7 +942,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Shams Azar FC</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -958,13 +958,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -973,7 +973,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -986,16 +986,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1004,29 +1004,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Gharafa SC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -1035,29 +1035,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
         <v>12</v>
       </c>
-      <c r="H11" t="n">
-        <v>11</v>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="12">
@@ -1066,29 +1066,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ulsan HD FC</t>
+          <t>Shabab Al Ahli</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
         <v>7</v>
       </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9</v>
-      </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1097,29 +1097,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Al Sadd SC</t>
+          <t>FC Pohang Steelers</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1128,20 +1128,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FC Pohang Steelers</t>
+          <t>Ulsan HD FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
@@ -1159,29 +1159,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Al Shamal SC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1190,26 +1190,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Beijing Guoan FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
         <v>-4</v>
@@ -1221,29 +1221,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Al Hilal Saudi FC</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="18">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Persepolis FC</t>
+          <t>Al Wakrah SC</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1268,13 +1268,13 @@
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="19">
@@ -1283,26 +1283,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sepahan SC</t>
+          <t>Al Ahli Saudi FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
         <v>-1</v>
@@ -1314,26 +1314,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ajman FC</t>
+          <t>AL Talaba SC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
         <v>-2</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Malavan Bandar FC</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1361,10 +1361,10 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
         <v>5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>7</v>
       </c>
       <c r="I21" t="n">
         <v>-2</v>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1392,13 +1392,13 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
       </c>
       <c r="I22" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="23">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rayong FC</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1426,10 +1426,10 @@
         <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="24">
@@ -1438,29 +1438,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Esteghlal FC</t>
+          <t>Persepolis FC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="25">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Al Shamal SC</t>
+          <t>Ajman FC</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1485,13 +1485,13 @@
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="26">
@@ -1500,29 +1500,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Al Shorta SC</t>
+          <t>FC Mashal Mubarek</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="29">
@@ -1628,29 +1628,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Ulsan HD FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1659,29 +1659,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Persepolis FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1690,29 +1690,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sepahan SC</t>
+          <t>Persepolis FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="8">
@@ -1747,19 +1747,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sepahan SC</t>
+          <t>Ulsan HD FC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1770,14 +1770,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sepahan SC</t>
+          <t>Ulsan HD FC</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1801,25 +1801,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sepahan SC</t>
+          <t>Ulsan HD FC</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1831,13 +1831,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sepahan SC</t>
+          <t>Ulsan HD FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1926,29 +1926,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Sadd SC</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1957,29 +1957,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al Hilal Saudi FC</t>
+          <t>Beijing Guoan FC</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="5">
@@ -1988,29 +1988,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Esteghlal FC</t>
+          <t>FC Mashal Mubarek</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="8">
@@ -2045,88 +2045,88 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Al Sadd SC</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Esteghlal FC</t>
+          <t>Beijing Guoan FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Al Hilal Saudi FC</t>
+          <t>FC Mashal Mubarek</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Esteghlal FC</t>
+          <t>Beijing Guoan FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Al Hilal Saudi FC</t>
+          <t>FC Mashal Mubarek</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Al Sadd SC</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Esteghlal FC</t>
+          <t>Beijing Guoan FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Al Sadd SC</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Esteghlal FC</t>
+          <t>Beijing Guoan FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Al Hilal Saudi FC</t>
+          <t>FC Mashal Mubarek</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -2135,19 +2135,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Al Sadd SC</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Al Hilal Saudi FC</t>
+          <t>FC Mashal Mubarek</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2224,29 +2224,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ulsan HD FC</t>
+          <t>FC Pohang Steelers</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2255,29 +2255,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Pohang Steelers</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2286,29 +2286,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="8">
@@ -2343,70 +2343,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ulsan HD FC</t>
+          <t>FC Pohang Steelers</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>FC Pohang Steelers</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ulsan HD FC</t>
-        </is>
-      </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FC Pohang Steelers</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ulsan HD FC</t>
+          <t>FC Pohang Steelers</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -2415,37 +2415,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ulsan HD FC</t>
+          <t>FC Pohang Steelers</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FC Pohang Steelers</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FC Pohang Steelers</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2522,26 +2522,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Gharafa SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="n">
         <v>5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -2553,29 +2553,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2584,29 +2584,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ajman FC</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="8">
@@ -2641,16 +2641,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ajman FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Gharafa SC</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -2659,91 +2659,91 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al Gharafa SC</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ajman FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Al Gharafa SC</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ajman FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Al Gharafa SC</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajman FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2820,29 +2820,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2851,29 +2851,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Al Ahli Saudi FC</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2898,13 +2898,13 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
@@ -2939,106 +2939,106 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Al Ahli Saudi FC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Al Ahli Saudi FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Al Ahli Saudi FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Al Ahli Saudi FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -3118,29 +3118,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Shabab Al Ahli</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3149,29 +3149,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3180,29 +3180,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al Shamal SC</t>
+          <t>Malavan Bandar FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="8">
@@ -3237,34 +3237,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Malavan Bandar FC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Shamal SC</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Shabab Al Ahli</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al Shamal SC</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -3273,52 +3273,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Shabab Al Ahli</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Malavan Bandar FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Al Shamal SC</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Malavan Bandar FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Al Shamal SC</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Shabab Al Ahli</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -3327,19 +3327,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Malavan Bandar FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Shabab Al Ahli</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3416,29 +3416,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Shams Azar FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3447,29 +3447,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wakrah SC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -3478,29 +3478,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rayong FC</t>
+          <t>AL Talaba SC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="8">
@@ -3535,16 +3535,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rayong FC</t>
+          <t>Al Wakrah SC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Shams Azar FC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -3553,34 +3553,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>AL Talaba SC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Shams Azar FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>AL Talaba SC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rayong FC</t>
+          <t>Al Wakrah SC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -3589,55 +3589,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Shams Azar FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rayong FC</t>
+          <t>Al Wakrah SC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Shams Azar FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>AL Talaba SC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rayong FC</t>
+          <t>Al Wakrah SC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>AL Talaba SC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3718,25 +3718,25 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="D3" t="n">
+      <c r="H3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -3745,29 +3745,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3780,22 +3780,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -3807,29 +3807,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="7">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3854,13 +3854,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -3888,10 +3888,10 @@
         <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3916,13 +3916,13 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
@@ -3931,29 +3931,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="11">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Shabab Al Ahli</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3975,16 +3975,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Persepolis FC</t>
+          <t>Beijing Guoan FC</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Al Sadd SC</t>
+          <t>Al Wakrah SC</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4040,10 +4040,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>-1</v>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FC Pohang Steelers</t>
+          <t>Ulsan HD FC</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4074,10 +4074,10 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="15">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ulsan HD FC</t>
+          <t>FC Pohang Steelers</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4102,13 +4102,13 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="16">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Shamal SC</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4133,13 +4133,13 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Al Hilal Saudi FC</t>
+          <t>Shams Azar FC</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4167,10 +4167,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="18">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Al Gharafa SC</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4195,13 +4195,13 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="21">
@@ -4241,119 +4241,119 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Persepolis FC</t>
+          <t>Al Wakrah SC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Shabab Al Ahli</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Al Sadd SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Beijing Guoan FC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>FC Pohang Steelers</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Al Gharafa SC</t>
+          <t>Al Shamal SC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Shams Azar FC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FC Pohang Steelers</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
@@ -4362,34 +4362,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Al Hilal Saudi FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -4398,88 +4398,88 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Al Nassr FC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Vissel Kobe</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Al Nassr FC</t>
-        </is>
-      </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
@@ -4488,37 +4488,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
